--- a/energy_sankey_data.xlsx
+++ b/energy_sankey_data.xlsx
@@ -18537,7 +18537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19559,11 +19559,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3. Why these charts differ from the IEA energy Sankey</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="58" customHeight="1">
+          <t>3. Comparability notes — primary-energy conventions (these appear as footnotes on each chart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="46" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Sweden 2023</t>
@@ -19571,29 +19571,96 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
+          <t>† Primary-energy convention (Eurostat physical energy content method): nuclear is shown as reactor heat, 485 PJ, of which about 36% becomes electricity; hydro, wind and solar are shown as generated electricity (1:1). Band widths are therefore not comparable across source types, and the rejected energy leaving the electricity node reflects this accounting convention rather than the relative efficiency of the sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Sweden 2023</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>‡ Cross-country comparison: the Swedish and Japanese charts follow different statistical conventions (see † above; Sweden also uses net calorific value, Japan gross). Band widths, totals and shares must not be compared between the two countries without adjustment — see the methodology panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Sweden 2024</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>† Primary-energy convention (Eurostat physical energy content method): nuclear is shown as reactor heat, 506 PJ, of which about 36% becomes electricity; hydro, wind and solar are shown as generated electricity (1:1). Band widths are therefore not comparable across source types, and the rejected energy leaving the electricity node reflects this accounting convention rather than the relative efficiency of the sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Japan FY2023</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>† Primary-energy convention (METI substitution method): nuclear, hydro, solar PV and wind are all converted to primary-energy equivalent at one uniform reference efficiency of 41.8%, so their band widths are mutually comparable but are about 2.4x the electricity actually generated. Geothermal is reported directly as heat. Rejected energy leaving the electricity node therefore includes this accounting artefact rather than only physical losses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Japan FY2024</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>† Primary-energy convention (METI substitution method): nuclear, hydro, solar PV and wind are all converted to primary-energy equivalent at one uniform reference efficiency of 42.4%, so their band widths are mutually comparable but are about 2.4x the electricity actually generated. Geothermal is reported directly as heat. Rejected energy leaving the electricity node therefore includes this accounting artefact rather than only physical losses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>4. Why these charts differ from the IEA energy Sankey</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Sweden 2023</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
           <t>IEA total energy supply 1,892 PJ vs 1,975 PJ here. Per fuel the two agree closely (biofuels &amp; waste 573.5 vs 570.4 PJ; hydro 238.3 vs 238.3; wind+solar+other 177.1 vs 177.1). Differences: the IEA imputes a fixed 33% nuclear efficiency (529 PJ) where Eurostat reports actual reactor heat ~36% (485 PJ), and the IEA headline nets out net electricity exports (-103 PJ) which this chart draws explicitly. The IEA's own by-source total is 1,983 PJ, within 0.4% of this chart.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="58" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Japan FY2023</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>IEA total energy supply 15,844 PJ (calendar 2023) vs METI 17,558 PJ (fiscal 2023). The ~1,714 PJ gap decomposes into: gross vs net calorific value ~+970 PJ (gas +354, oil +409, coal +204); METI's substitution method for hydro/solar/wind ~+916 PJ (implied factor 41.8%), offset by nuclear -193 PJ and geothermal -93 PJ; recovered energy (未活用エネルギー) counted only by METI +273 PJ; and fiscal vs calendar year timing plus LHV conversion of biomass, about -150 PJ.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="58" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="55" ht="58" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Because Japanese band widths represent throughput including stock change and intra-band transformation, the bands sum to slightly more than METI's domestic-supply headline (17,629 vs 17,558 PJ in FY2023, a 0.4% difference). Cite METI's headline figure.</t>
         </is>

--- a/energy_sankey_data.xlsx
+++ b/energy_sankey_data.xlsx
@@ -18537,7 +18537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19583,84 +19583,132 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>‡ Cross-country comparison: the Swedish and Japanese charts follow different statistical conventions (see † above; Sweden also uses net calorific value, Japan gross). Band widths, totals and shares must not be compared between the two countries without adjustment — see the methodology panel.</t>
+          <t>‡ Biomass and waste scope: Eurostat splits municipal waste, so the biogenic half (36 PJ) sits inside this biomass band while the fossil half is drawn separately as non-renewable waste. Biomass here also includes 66 PJ of liquid transport biofuels. Japan does not split municipal waste and excludes it from biomass altogether, so neither the biomass nor the waste bands mean the same thing in the two charts.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="46" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Sweden 2024</t>
+          <t>Sweden 2023</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>† Primary-energy convention (Eurostat physical energy content method): nuclear is shown as reactor heat, 506 PJ, of which about 36% becomes electricity; hydro, wind and solar are shown as generated electricity (1:1). Band widths are therefore not comparable across source types, and the rejected energy leaving the electricity node reflects this accounting convention rather than the relative efficiency of the sources.</t>
+          <t>§ Cross-country comparison: the Swedish and Japanese charts follow different statistical conventions (see † and ‡ above; Sweden also uses net calorific value, Japan gross). Band widths, totals and shares must not be compared between the two countries without adjustment — see the methodology panel.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="46" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Japan FY2023</t>
+          <t>Sweden 2024</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>† Primary-energy convention (METI substitution method): nuclear, hydro, solar PV and wind are all converted to primary-energy equivalent at one uniform reference efficiency of 41.8%, so their band widths are mutually comparable but are about 2.4x the electricity actually generated. Geothermal is reported directly as heat. Rejected energy leaving the electricity node therefore includes this accounting artefact rather than only physical losses.</t>
+          <t>† Primary-energy convention (Eurostat physical energy content method): nuclear is shown as reactor heat, 506 PJ, of which about 36% becomes electricity; hydro, wind and solar are shown as generated electricity (1:1). Band widths are therefore not comparable across source types, and the rejected energy leaving the electricity node reflects this accounting convention rather than the relative efficiency of the sources.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>Sweden 2024</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>‡ Biomass and waste scope: Eurostat splits municipal waste, so the biogenic half (36 PJ) sits inside this biomass band while the fossil half is drawn separately as non-renewable waste. Biomass here also includes 33 PJ of liquid transport biofuels. Japan does not split municipal waste and excludes it from biomass altogether, so neither the biomass nor the waste bands mean the same thing in the two charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Japan FY2023</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>† Primary-energy convention (METI substitution method): nuclear, hydro, solar PV and wind are all converted to primary-energy equivalent at one uniform reference efficiency of 41.8%, so their band widths are mutually comparable but are about 2.4x the electricity actually generated. Geothermal is reported directly as heat. Rejected energy leaving the electricity node therefore includes this accounting artefact rather than only physical losses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="46" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Japan FY2023</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>‡ Biomass and waste scope: biomass here excludes municipal waste, which sits — biogenic and fossil fractions alike, unsplit — in waste &amp; recovered energy (282 PJ of refuse fuels). That band also holds 273 PJ of recovered industrial steam and electricity, which is not a waste fuel at all. The 20 PJ of bioethanol is blended upstream and reaches transport inside the oil band, so no biomass flows to transport here. Sweden splits municipal waste and shows transport biofuels within biomass, so neither band means the same thing in the two charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="46" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>Japan FY2024</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>† Primary-energy convention (METI substitution method): nuclear, hydro, solar PV and wind are all converted to primary-energy equivalent at one uniform reference efficiency of 42.4%, so their band widths are mutually comparable but are about 2.4x the electricity actually generated. Geothermal is reported directly as heat. Rejected energy leaving the electricity node therefore includes this accounting artefact rather than only physical losses.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Japan FY2024</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>‡ Biomass and waste scope: biomass here excludes municipal waste, which sits — biogenic and fossil fractions alike, unsplit — in waste &amp; recovered energy (318 PJ of refuse fuels). That band also holds 256 PJ of recovered industrial steam and electricity, which is not a waste fuel at all. The 20 PJ of bioethanol is blended upstream and reaches transport inside the oil band, so no biomass flows to transport here. Sweden splits municipal waste and shows transport biofuels within biomass, so neither band means the same thing in the two charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>4. Why these charts differ from the IEA energy Sankey</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="58" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="57" ht="58" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Sweden 2023</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>IEA total energy supply 1,892 PJ vs 1,975 PJ here. Per fuel the two agree closely (biofuels &amp; waste 573.5 vs 570.4 PJ; hydro 238.3 vs 238.3; wind+solar+other 177.1 vs 177.1). Differences: the IEA imputes a fixed 33% nuclear efficiency (529 PJ) where Eurostat reports actual reactor heat ~36% (485 PJ), and the IEA headline nets out net electricity exports (-103 PJ) which this chart draws explicitly. The IEA's own by-source total is 1,983 PJ, within 0.4% of this chart.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="58" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="58" ht="58" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Japan FY2023</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>IEA total energy supply 15,844 PJ (calendar 2023) vs METI 17,558 PJ (fiscal 2023). The ~1,714 PJ gap decomposes into: gross vs net calorific value ~+970 PJ (gas +354, oil +409, coal +204); METI's substitution method for hydro/solar/wind ~+916 PJ (implied factor 41.8%), offset by nuclear -193 PJ and geothermal -93 PJ; recovered energy (未活用エネルギー) counted only by METI +273 PJ; and fiscal vs calendar year timing plus LHV conversion of biomass, about -150 PJ.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="58" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="59" ht="58" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Because Japanese band widths represent throughput including stock change and intra-band transformation, the bands sum to slightly more than METI's domestic-supply headline (17,629 vs 17,558 PJ in FY2023, a 0.4% difference). Cite METI's headline figure.</t>
         </is>
